--- a/data/trans_dic/P32E$bar_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32E$bar_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,21; 94,07</t>
+          <t>32,36; 93,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,95; 90,0</t>
+          <t>52,28; 88,91</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>46,54; 92,93</t>
+          <t>48,07; 92,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93,05; 100,0</t>
+          <t>92,85; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,66; 95,06</t>
+          <t>61,28; 95,13</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44,22; 80,61</t>
+          <t>41,26; 80,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,49; 100,0</t>
+          <t>35,21; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,86; 83,1</t>
+          <t>49,0; 81,46</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,12; 86,05</t>
+          <t>51,66; 86,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,53; 94,7</t>
+          <t>52,67; 94,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,61; 84,09</t>
+          <t>57,1; 84,32</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,46; 80,72</t>
+          <t>43,1; 79,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,23; 63,29</t>
+          <t>8,33; 58,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,72; 71,32</t>
+          <t>39,46; 71,61</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,78; 70,55</t>
+          <t>23,98; 68,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,22; 100,0</t>
+          <t>38,88; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32,58; 71,53</t>
+          <t>35,35; 72,57</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,61; 85,26</t>
+          <t>12,57; 86,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,71; 75,09</t>
+          <t>8,92; 72,3</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>57,44; 74,16</t>
+          <t>58,04; 75,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>58,81; 83,98</t>
+          <t>59,73; 84,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61,77; 74,96</t>
+          <t>61,79; 75,46</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en bares, pub o restaurantes (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5252; 14441</t>
+          <t>4968; 14356</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21299; 36895</t>
+          <t>21434; 36450</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10687; 21342</t>
+          <t>11038; 21135</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12600; 13540</t>
+          <t>12572; 13540</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23237; 34700</t>
+          <t>22369; 34726</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11877; 21649</t>
+          <t>11080; 21587</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1881; 5453</t>
+          <t>1920; 5453</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16109; 26848</t>
+          <t>15830; 26320</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14104; 23741</t>
+          <t>14252; 23879</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4747; 8558</t>
+          <t>4760; 8553</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20369; 30799</t>
+          <t>20915; 30884</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9420; 18337</t>
+          <t>9791; 18110</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>503; 3871</t>
+          <t>509; 3592</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11452; 20565</t>
+          <t>11379; 20647</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3548; 9347</t>
+          <t>3178; 9016</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1329; 3478</t>
+          <t>1352; 3478</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5450; 11965</t>
+          <t>5913; 12139</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>642; 4340</t>
+          <t>640; 4419</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>595; 5127</t>
+          <t>609; 4937</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>82776; 106876</t>
+          <t>83638; 108288</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32177; 45948</t>
+          <t>32683; 46372</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>122822; 149033</t>
+          <t>122849; 150025</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$bar_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32E$bar_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>76,88%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46,23; 93,24</t>
+          <t>49,98; 94,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,36; 93,51</t>
+          <t>37,86; 94,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52,28; 88,91</t>
+          <t>56,08; 91,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,07; 92,04</t>
+          <t>49,49; 90,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,85; 100,0</t>
+          <t>68,74; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,28; 95,13</t>
+          <t>62,22; 93,07</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>61,83%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,26; 80,38</t>
+          <t>39,15; 77,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,21; 100,0</t>
+          <t>38,24; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,0; 81,46</t>
+          <t>43,27; 78,18</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,66; 86,55</t>
+          <t>47,96; 83,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,67; 94,64</t>
+          <t>45,68; 89,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,1; 84,32</t>
+          <t>53,0; 81,6</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,3%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,1; 79,72</t>
+          <t>43,01; 79,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,33; 58,71</t>
+          <t>7,9; 63,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,46; 71,61</t>
+          <t>39,65; 71,07</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,98; 68,05</t>
+          <t>22,14; 67,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,88; 100,0</t>
+          <t>35,7; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,35; 72,57</t>
+          <t>36,63; 74,04</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,57; 86,81</t>
+          <t>11,19; 81,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,92; 72,3</t>
+          <t>6,71; 68,84</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>67,53%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>58,04; 75,14</t>
+          <t>56,91; 72,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>59,73; 84,75</t>
+          <t>58,67; 81,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61,79; 75,46</t>
+          <t>60,83; 73,8</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19533</t>
+          <t>22961</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>13567</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30416</t>
+          <t>36528</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11856; 23909</t>
+          <t>14771; 27911</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4968; 14356</t>
+          <t>6799; 17006</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21434; 36450</t>
+          <t>26644; 43441</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30575</t>
+          <t>35866</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11038; 21135</t>
+          <t>13819; 25259</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12572; 13540</t>
+          <t>10979; 15972</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22369; 34726</t>
+          <t>27314; 40852</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21588</t>
+          <t>22430</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11080; 21587</t>
+          <t>11622; 22920</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1920; 5453</t>
+          <t>2520; 6589</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15830; 26320</t>
+          <t>15697; 28360</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26719</t>
+          <t>28551</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14252; 23879</t>
+          <t>14611; 25493</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4760; 8553</t>
+          <t>4905; 9608</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20915; 30884</t>
+          <t>21839; 33625</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>16564</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9791; 18110</t>
+          <t>9996; 18452</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>509; 3592</t>
+          <t>530; 4286</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11379; 20647</t>
+          <t>11876; 21287</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9828</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3178; 9016</t>
+          <t>3205; 9708</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1352; 3478</t>
+          <t>1374; 3848</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5913; 12139</t>
+          <t>6710; 13563</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2632</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>640; 4419</t>
+          <t>688; 5010</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>609; 4937</t>
+          <t>571; 5858</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>95952</t>
+          <t>106085</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>46314</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>136649</t>
+          <t>152399</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>83638; 108288</t>
+          <t>91893; 117638</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32683; 46372</t>
+          <t>37657; 52305</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>122849; 150025</t>
+          <t>137276; 166546</t>
         </is>
       </c>
     </row>
